--- a/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF8CB13-C17B-A245-874D-6D121508AE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF54DA5-E8C0-CA40-B399-F9DF0D339D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="760" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="4460" yWindow="3960" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
   <si>
     <t>Endogenos</t>
   </si>
@@ -47,48 +47,21 @@
     <t>LysoPC</t>
   </si>
   <si>
-    <t>deuterated-LysoPC (18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-LysoPE (18:1(d7))</t>
-  </si>
-  <si>
     <t>LPC (20:0)</t>
   </si>
   <si>
     <t>SM</t>
   </si>
   <si>
-    <t>deuterated-PG (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-SM (d18:1/18:1(d9))</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
-    <t>deuterated-PC (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-PE (15:0/18:1(d7))</t>
-  </si>
-  <si>
-    <t>deuterated-DG (15:0/18:1(d7))</t>
-  </si>
-  <si>
     <t>HexCer</t>
   </si>
   <si>
     <t>TG</t>
   </si>
   <si>
-    <t>deuterated-TAG (15:0/18:1(d7))/15:0)</t>
-  </si>
-  <si>
-    <t>deuterated-Chol Ester (18:1(d7))</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -101,9 +74,6 @@
     <t>RT</t>
   </si>
   <si>
-    <t>Deuterated</t>
-  </si>
-  <si>
     <t>mz</t>
   </si>
   <si>
@@ -113,36 +83,9 @@
     <t>CAR</t>
   </si>
   <si>
-    <t>dLysoPC</t>
-  </si>
-  <si>
-    <t>dLysoPE</t>
-  </si>
-  <si>
     <t>LPC</t>
   </si>
   <si>
-    <t>dPG</t>
-  </si>
-  <si>
-    <t>dSM</t>
-  </si>
-  <si>
-    <t>dPC</t>
-  </si>
-  <si>
-    <t>dPE</t>
-  </si>
-  <si>
-    <t>dDG</t>
-  </si>
-  <si>
-    <t>dTG</t>
-  </si>
-  <si>
-    <t>dCE</t>
-  </si>
-  <si>
     <t>short_name</t>
   </si>
   <si>
@@ -150,6 +93,78 @@
   </si>
   <si>
     <t>TG1</t>
+  </si>
+  <si>
+    <t>PC(15:0/18:1)</t>
+  </si>
+  <si>
+    <t>LPC(0:0/18:1)</t>
+  </si>
+  <si>
+    <t>LPC(18:1/0:0)</t>
+  </si>
+  <si>
+    <t>PE(15:0/18:1)</t>
+  </si>
+  <si>
+    <t>LPE(18:1/0:0)</t>
+  </si>
+  <si>
+    <t>LPE(0:0/18:1)</t>
+  </si>
+  <si>
+    <t>TG(15:0/18:1/15:0)</t>
+  </si>
+  <si>
+    <t>DG(15:0/18:1)</t>
+  </si>
+  <si>
+    <t>SM(d18:1/18:1)</t>
+  </si>
+  <si>
+    <t>Cer(d18:1/15:0)</t>
+  </si>
+  <si>
+    <t>C17 Sphinganine</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c </t>
+  </si>
+  <si>
+    <t xml:space="preserve">d </t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l </t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>cernh4</t>
   </si>
 </sst>
 </file>
@@ -567,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -575,22 +590,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -607,11 +622,10 @@
         <v>0.8</v>
       </c>
       <c r="E2">
-        <f>D2*60</f>
         <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -630,7 +644,6 @@
         <v>2.56</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E18" si="0">D3*60</f>
         <v>153.6</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -641,46 +654,44 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="8">
-        <v>529.39940000000001</v>
+        <v>552.40239999999994</v>
       </c>
       <c r="D4" s="9">
-        <v>2.7429999999999999</v>
+        <v>4.24</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>164.57999999999998</v>
+        <v>254.4</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="8">
-        <v>487.35239999999999</v>
+        <v>701.55920000000003</v>
       </c>
       <c r="D5" s="9">
-        <v>2.8479999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>170.88</v>
+        <v>371.40000000000003</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -693,17 +704,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="5">
-        <v>552.40239999999994</v>
+        <v>758.56939999999997</v>
       </c>
       <c r="D6" s="7">
-        <v>4.24</v>
+        <v>7.76</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>254.4</v>
+        <v>465.59999999999997</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
@@ -713,66 +723,63 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5">
-        <v>701.55920000000003</v>
+        <v>759.63879999999995</v>
       </c>
       <c r="D7" s="7">
-        <v>6.19</v>
+        <v>11.43</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>371.40000000000003</v>
+        <v>685.8</v>
       </c>
       <c r="F7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="8">
-        <v>759.58749999999998</v>
+        <v>812.69740000000002</v>
       </c>
       <c r="D8" s="9">
-        <v>6.46</v>
+        <v>12.25</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>387.6</v>
+        <v>735</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="8">
-        <v>738.64700000000005</v>
+        <v>900.80150000000003</v>
       </c>
       <c r="D9" s="9">
-        <v>7.2709999999999999</v>
+        <v>13.97</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>436.26</v>
+        <v>838.2</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
@@ -782,40 +789,38 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5">
-        <v>758.56939999999997</v>
+        <v>880.83274340259902</v>
       </c>
       <c r="D10" s="7">
-        <v>7.76</v>
+        <v>16.05</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>465.59999999999997</v>
+        <v>963</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C11" s="8">
-        <v>753.61339999999996</v>
+        <v>746.57003999999995</v>
       </c>
       <c r="D11" s="9">
-        <v>8.1709999999999994</v>
+        <v>7.91</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>490.26</v>
+        <v>474.6</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -825,20 +830,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" s="8">
-        <v>711.56640000000004</v>
+        <v>521.34810000000004</v>
       </c>
       <c r="D12" s="9">
-        <v>8.5030000000000001</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>510.18</v>
+        <v>148.20000000000002</v>
       </c>
       <c r="F12" t="s">
         <v>31</v>
@@ -848,161 +852,214 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8">
-        <v>759.63879999999995</v>
+        <v>521.34810000000004</v>
       </c>
       <c r="D13" s="10">
-        <v>11.43</v>
+        <v>2.71</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>685.8</v>
+        <v>162.6</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C14" s="8">
-        <v>605.58439999999996</v>
+        <v>704.52314000000001</v>
       </c>
       <c r="D14" s="9">
-        <v>11.68</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>700.8</v>
+        <v>498.00000000000006</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C15" s="5">
-        <v>812.69740000000002</v>
+        <v>480.30904000000004</v>
       </c>
       <c r="D15" s="7">
-        <v>12.25</v>
+        <v>2.8010000000000002</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
-        <v>735</v>
+        <v>168.06</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C16" s="5">
-        <v>900.80150000000003</v>
+        <v>480.30904000000004</v>
       </c>
       <c r="D16" s="7">
-        <v>13.97</v>
+        <v>2.6</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
-        <v>838.2</v>
+        <v>156</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C17" s="8">
-        <v>829.79849999999999</v>
+        <v>805.72853999999995</v>
       </c>
       <c r="D17" s="9">
-        <v>13.997999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
-        <v>839.88</v>
+        <v>834</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C18" s="8">
-        <v>675.67790000000002</v>
+        <v>598.54560000000004</v>
       </c>
       <c r="D18" s="9">
-        <v>15.46</v>
+        <v>11.61</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
-        <v>927.6</v>
+        <v>696.59999999999991</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C19" s="8">
-        <v>880.83274340259902</v>
+        <v>729.59114</v>
       </c>
       <c r="D19" s="9">
-        <v>16.05</v>
+        <v>7.16</v>
       </c>
       <c r="E19">
-        <f>D19*60</f>
-        <v>963</v>
+        <v>429.6</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>524.50433999999996</v>
+      </c>
+      <c r="D20">
+        <v>7.7</v>
+      </c>
+      <c r="E20">
+        <v>462</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>288.28969999999998</v>
+      </c>
+      <c r="D21">
+        <v>1.79</v>
+      </c>
+      <c r="E21">
+        <v>107.4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>541.53539999999998</v>
+      </c>
+      <c r="D22">
+        <v>7.7</v>
+      </c>
+      <c r="E22">
+        <v>462</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF54DA5-E8C0-CA40-B399-F9DF0D339D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CA0B8A-A3D2-904A-A8B9-E03662387F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4460" yWindow="3960" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="4460" yWindow="1140" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
   <si>
     <t>Endogenos</t>
   </si>
@@ -165,6 +165,18 @@
   </si>
   <si>
     <t>cernh4</t>
+  </si>
+  <si>
+    <t>Cer(d40:2)</t>
+  </si>
+  <si>
+    <t>Cer</t>
+  </si>
+  <si>
+    <t>ISTD</t>
+  </si>
+  <si>
+    <t>Sphinganine</t>
   </si>
 </sst>
 </file>
@@ -174,7 +186,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -205,6 +217,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -226,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -248,6 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -1062,6 +1081,46 @@
         <v>42</v>
       </c>
     </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="11">
+        <v>678.65070000000003</v>
+      </c>
+      <c r="D23" s="11">
+        <v>12</v>
+      </c>
+      <c r="E23" s="11">
+        <v>720</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="11">
+        <v>288.28969999999998</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1.99</v>
+      </c>
+      <c r="E24" s="11">
+        <v>119.4</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CA0B8A-A3D2-904A-A8B9-E03662387F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF41C29-C696-4D4F-B213-F434E7EAEBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4460" yWindow="1140" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="17060" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
   <si>
     <t>Endogenos</t>
   </si>
@@ -158,9 +158,6 @@
     <t xml:space="preserve">l </t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>Light</t>
   </si>
   <si>
@@ -177,6 +174,42 @@
   </si>
   <si>
     <t>Sphinganine</t>
+  </si>
+  <si>
+    <t>LIPID SUBCLASS [ABBREV]</t>
+  </si>
+  <si>
+    <t>Ceramides [Cer]</t>
+  </si>
+  <si>
+    <t>Dilglycerides [DG]</t>
+  </si>
+  <si>
+    <t>Monoacylglycerophosphocholines [LPC]</t>
+  </si>
+  <si>
+    <t>Monoacylglycerophosphoethanolamines [LPE]</t>
+  </si>
+  <si>
+    <t>Diacylglycerophosphocholines [PC]</t>
+  </si>
+  <si>
+    <t>Carnitines [CAR]</t>
+  </si>
+  <si>
+    <t>Sphingomyelins [SM]</t>
+  </si>
+  <si>
+    <t>Triglycerides [TG]</t>
+  </si>
+  <si>
+    <t>Diacylglycerophosphoethanolamines [PE]</t>
+  </si>
+  <si>
+    <t>Hexosylceramides [HexCer]</t>
+  </si>
+  <si>
+    <t>Sphingoid bases [SPB]</t>
   </si>
 </sst>
 </file>
@@ -601,10 +634,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -626,6 +660,9 @@
       <c r="F1" t="s">
         <v>16</v>
       </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -646,6 +683,9 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
+      <c r="G2" t="s">
+        <v>52</v>
+      </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
@@ -668,6 +708,9 @@
       <c r="F3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
@@ -690,6 +733,9 @@
       <c r="F4" t="s">
         <v>15</v>
       </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
@@ -712,6 +758,9 @@
       <c r="F5" t="s">
         <v>4</v>
       </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
@@ -734,6 +783,9 @@
       <c r="F6" t="s">
         <v>5</v>
       </c>
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
@@ -756,6 +808,9 @@
       <c r="F7" t="s">
         <v>13</v>
       </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
@@ -778,6 +833,9 @@
       <c r="F8" t="s">
         <v>6</v>
       </c>
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
@@ -800,6 +858,9 @@
       <c r="F9" t="s">
         <v>7</v>
       </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
@@ -822,12 +883,15 @@
       <c r="F10" t="s">
         <v>18</v>
       </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>19</v>
@@ -844,12 +908,15 @@
       <c r="F11" t="s">
         <v>30</v>
       </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>20</v>
@@ -866,12 +933,15 @@
       <c r="F12" t="s">
         <v>31</v>
       </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>21</v>
@@ -888,12 +958,15 @@
       <c r="F13" t="s">
         <v>32</v>
       </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>22</v>
@@ -910,12 +983,15 @@
       <c r="F14" t="s">
         <v>33</v>
       </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>23</v>
@@ -932,12 +1008,15 @@
       <c r="F15" t="s">
         <v>34</v>
       </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>24</v>
@@ -954,12 +1033,15 @@
       <c r="F16" t="s">
         <v>35</v>
       </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>25</v>
@@ -976,12 +1058,15 @@
       <c r="F17" t="s">
         <v>36</v>
       </c>
+      <c r="G17" t="s">
+        <v>54</v>
+      </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
@@ -998,12 +1083,15 @@
       <c r="F18" t="s">
         <v>37</v>
       </c>
+      <c r="G18" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -1020,10 +1108,13 @@
       <c r="F19" t="s">
         <v>38</v>
       </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
         <v>28</v>
@@ -1040,85 +1131,77 @@
       <c r="F20" t="s">
         <v>39</v>
       </c>
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>541.53539999999998</v>
+      </c>
+      <c r="D21">
+        <v>7.7</v>
+      </c>
+      <c r="E21">
+        <v>462</v>
+      </c>
+      <c r="F21" t="s">
         <v>41</v>
       </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21">
-        <v>288.28969999999998</v>
-      </c>
-      <c r="D21">
-        <v>1.79</v>
-      </c>
-      <c r="E21">
-        <v>107.4</v>
-      </c>
-      <c r="F21" t="s">
-        <v>40</v>
+      <c r="G21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22">
-        <v>541.53539999999998</v>
-      </c>
-      <c r="D22">
-        <v>7.7</v>
-      </c>
-      <c r="E22">
-        <v>462</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="A22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>42</v>
+      </c>
+      <c r="C22" s="11">
+        <v>678.65070000000003</v>
+      </c>
+      <c r="D22" s="11">
+        <v>12</v>
+      </c>
+      <c r="E22" s="11">
+        <v>720</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C23" s="11">
-        <v>678.65070000000003</v>
+        <v>288.28969999999998</v>
       </c>
       <c r="D23" s="11">
-        <v>12</v>
+        <v>1.99</v>
       </c>
       <c r="E23" s="11">
-        <v>720</v>
+        <v>119.4</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="11">
-        <v>288.28969999999998</v>
-      </c>
-      <c r="D24" s="11">
-        <v>1.99</v>
-      </c>
-      <c r="E24" s="11">
-        <v>119.4</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>46</v>
+      <c r="G23" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF41C29-C696-4D4F-B213-F434E7EAEBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2C2042-8C45-4648-822F-9DFE435FEFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14680" yWindow="660" windowWidth="14720" windowHeight="17060" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="8880" yWindow="660" windowWidth="20520" windowHeight="17060" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>Endogenos</t>
   </si>
@@ -210,6 +210,21 @@
   </si>
   <si>
     <t>Sphingoid bases [SPB]</t>
+  </si>
+  <si>
+    <t>LPC(0:0/16:0)</t>
+  </si>
+  <si>
+    <t>SM(d18:2/16:0)</t>
+  </si>
+  <si>
+    <t>PC(16:0/18:2)</t>
+  </si>
+  <si>
+    <t>TG(54:4)</t>
+  </si>
+  <si>
+    <t>SM(d18:1/20:0)</t>
   </si>
 </sst>
 </file>
@@ -694,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="C3" s="5">
         <v>496.33980000000003</v>
@@ -744,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="C5" s="8">
         <v>701.55920000000003</v>
@@ -769,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5">
         <v>758.56939999999997</v>
@@ -794,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="C7" s="5">
         <v>759.63879999999995</v>
@@ -844,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="C9" s="8">
         <v>900.80150000000003</v>

--- a/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/exercise_study/positive/pos_lipid_reference_set.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/exercise_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AA16C7-2696-A04E-B5A5-BF5479FC615C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1274529A-D068-BF4B-87FF-4B33CEDB3DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14680" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -836,7 +836,7 @@
         <v>2.62</v>
       </c>
       <c r="E12" s="7">
-        <v>148.20000000000002</v>
+        <v>157.20000000000002</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>33</v>
@@ -858,7 +858,7 @@
         <v>2.8</v>
       </c>
       <c r="E13" s="7">
-        <v>162.6</v>
+        <v>168</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>34</v>
@@ -880,7 +880,7 @@
         <v>2.9</v>
       </c>
       <c r="E14" s="7">
-        <v>168.06</v>
+        <v>174</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>38</v>
@@ -902,7 +902,7 @@
         <v>2.75</v>
       </c>
       <c r="E15" s="7">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>37</v>
@@ -924,13 +924,14 @@
         <v>7.77</v>
       </c>
       <c r="E16" s="7">
-        <v>429.6</v>
+        <v>466.2</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -943,12 +944,13 @@
       <c r="D17" s="6">
         <v>1.99</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="7">
         <v>119.4</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="G17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
